--- a/week3/manual_gold/920100_三协电机_gold.xlsx
+++ b/week3/manual_gold/920100_三协电机_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +512,11 @@
           <t>2022年7月，向稳正景明和长泽创投定向发行股票530万股，每股4.48元</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +559,11 @@
           <t>长泽创投认购，合计530万股</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,6 +606,11 @@
           <t>发行股数530万股，每股4.48元，募集资金总额2374.40万元，完成后注册资本3530万元</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +653,11 @@
           <t>2023年8月，实际发行318.5万股，增发价格5.41元/股，完成后股本增至3848.50万元</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -668,6 +698,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>2023年11月，每10股转增3.8股，总股本增至5310.93万股</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -682,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,6 +771,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -788,6 +828,11 @@
           <t>发行前盛祎持股62.97%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -840,6 +885,11 @@
           <t>朱绶青持股19.49%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -892,6 +942,11 @@
           <t>稳正景明持股9.16%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -944,6 +999,11 @@
           <t>长泽创投持股4.61%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -996,6 +1056,11 @@
           <t>盛月瑶持股1.01%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1048,6 +1113,11 @@
           <t>盛松持股0.39%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1100,6 +1170,11 @@
           <t>薛小丽持股0.39%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1152,6 +1227,11 @@
           <t>倪进宽持股0.39%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1204,6 +1284,11 @@
           <t>余方成持股0.39%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,6 +1339,11 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>吴春扣持股0.26%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,6 +1535,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1487,6 +1582,11 @@
           <t>发行人历史沿革中存在股权代持情况，2021年3月上述股权代持已解除，涉及代持各方没找到纠纷或潜在纠纷</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1529,6 +1629,7 @@
           <t>翻遍了正文，发行人层面除代持解除外无其他股权转让。要补全得去翻公转说明书</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
